--- a/DATA PEGAWAI/JADWAL KARYAWAN.xlsx
+++ b/DATA PEGAWAI/JADWAL KARYAWAN.xlsx
@@ -1702,9 +1702,6 @@
     <t>dr. Muhammad Fauzi Saputra, Sp.An</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>NIP</t>
   </si>
   <si>
@@ -2093,6 +2090,9 @@
   </si>
   <si>
     <t>Koordinator Farmasi</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -2512,16 +2512,16 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>561</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>562</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
@@ -2650,7 +2650,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>10</v>
@@ -2757,7 +2757,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
@@ -2864,7 +2864,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>12</v>
@@ -2971,7 +2971,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
@@ -3185,7 +3185,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>10</v>
@@ -3292,7 +3292,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>10</v>
@@ -3506,7 +3506,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>10</v>
@@ -3613,7 +3613,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>10</v>
@@ -3720,7 +3720,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>10</v>
@@ -3827,7 +3827,7 @@
         <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>11</v>
@@ -3934,7 +3934,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>12</v>
@@ -4041,7 +4041,7 @@
         <v>42</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>10</v>
@@ -4148,7 +4148,7 @@
         <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>10</v>
@@ -4255,7 +4255,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>10</v>
@@ -4362,7 +4362,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>10</v>
@@ -4469,7 +4469,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>10</v>
@@ -4576,7 +4576,7 @@
         <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>10</v>
@@ -4683,7 +4683,7 @@
         <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>10</v>
@@ -4790,7 +4790,7 @@
         <v>55</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>10</v>
@@ -4897,7 +4897,7 @@
         <v>57</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>10</v>
@@ -5004,7 +5004,7 @@
         <v>59</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>10</v>
@@ -5111,7 +5111,7 @@
         <v>61</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>10</v>
@@ -5218,7 +5218,7 @@
         <v>63</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>64</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>10</v>
@@ -5432,7 +5432,7 @@
         <v>65</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>10</v>
@@ -5539,7 +5539,7 @@
         <v>67</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>10</v>
@@ -5646,7 +5646,7 @@
         <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>10</v>
@@ -5753,7 +5753,7 @@
         <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>10</v>
@@ -5860,7 +5860,7 @@
         <v>73</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>10</v>
@@ -5967,7 +5967,7 @@
         <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>10</v>
@@ -6074,7 +6074,7 @@
         <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>10</v>
@@ -6181,7 +6181,7 @@
         <v>79</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>10</v>
@@ -6288,7 +6288,7 @@
         <v>81</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>10</v>
@@ -6395,7 +6395,7 @@
         <v>83</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>10</v>
@@ -6502,7 +6502,7 @@
         <v>85</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>10</v>
@@ -6609,7 +6609,7 @@
         <v>87</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>10</v>
@@ -6716,7 +6716,7 @@
         <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>10</v>
@@ -6823,7 +6823,7 @@
         <v>91</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>10</v>
@@ -6930,7 +6930,7 @@
         <v>93</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>10</v>
@@ -7037,7 +7037,7 @@
         <v>95</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>10</v>
@@ -7144,7 +7144,7 @@
         <v>97</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>10</v>
@@ -7251,7 +7251,7 @@
         <v>99</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>10</v>
@@ -7358,7 +7358,7 @@
         <v>101</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>10</v>
@@ -7465,7 +7465,7 @@
         <v>103</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>10</v>
@@ -7572,7 +7572,7 @@
         <v>105</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>10</v>
@@ -7679,7 +7679,7 @@
         <v>107</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>10</v>
@@ -7786,7 +7786,7 @@
         <v>109</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>10</v>
@@ -7893,7 +7893,7 @@
         <v>111</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>113</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>10</v>
@@ -8107,7 +8107,7 @@
         <v>115</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>10</v>
@@ -8214,7 +8214,7 @@
         <v>117</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>10</v>
@@ -8321,7 +8321,7 @@
         <v>119</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>10</v>
@@ -8428,7 +8428,7 @@
         <v>121</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>10</v>
@@ -8535,7 +8535,7 @@
         <v>123</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>10</v>
@@ -8642,7 +8642,7 @@
         <v>125</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>10</v>
@@ -8749,7 +8749,7 @@
         <v>127</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>10</v>
@@ -8856,7 +8856,7 @@
         <v>129</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>10</v>
@@ -8963,7 +8963,7 @@
         <v>131</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>10</v>
@@ -9070,7 +9070,7 @@
         <v>133</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>10</v>
@@ -9177,7 +9177,7 @@
         <v>135</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>10</v>
@@ -9284,7 +9284,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>10</v>
@@ -9391,7 +9391,7 @@
         <v>139</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>10</v>
@@ -9498,7 +9498,7 @@
         <v>141</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>10</v>
@@ -9605,7 +9605,7 @@
         <v>143</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>10</v>
@@ -9712,7 +9712,7 @@
         <v>145</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>10</v>
@@ -9819,7 +9819,7 @@
         <v>147</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>10</v>
@@ -9926,7 +9926,7 @@
         <v>149</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>10</v>
@@ -10033,7 +10033,7 @@
         <v>151</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>10</v>
@@ -10140,7 +10140,7 @@
         <v>153</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>10</v>
@@ -10247,7 +10247,7 @@
         <v>155</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>10</v>
@@ -10354,7 +10354,7 @@
         <v>157</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>159</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>10</v>
@@ -10568,7 +10568,7 @@
         <v>161</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>10</v>
@@ -10675,7 +10675,7 @@
         <v>162</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>10</v>
@@ -10782,7 +10782,7 @@
         <v>163</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>10</v>
@@ -10889,7 +10889,7 @@
         <v>164</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>10</v>
@@ -10996,7 +10996,7 @@
         <v>165</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>10</v>
@@ -11103,7 +11103,7 @@
         <v>166</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>10</v>
@@ -11210,7 +11210,7 @@
         <v>167</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>10</v>
@@ -11317,7 +11317,7 @@
         <v>168</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>10</v>
@@ -11424,7 +11424,7 @@
         <v>170</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>10</v>
@@ -11531,7 +11531,7 @@
         <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>10</v>
@@ -11638,7 +11638,7 @@
         <v>174</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>10</v>
@@ -11745,7 +11745,7 @@
         <v>176</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>10</v>
@@ -11852,7 +11852,7 @@
         <v>178</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>10</v>
@@ -11959,7 +11959,7 @@
         <v>180</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>10</v>
@@ -12066,7 +12066,7 @@
         <v>182</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>10</v>
@@ -12173,7 +12173,7 @@
         <v>183</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>10</v>
@@ -12280,7 +12280,7 @@
         <v>185</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>10</v>
@@ -12387,7 +12387,7 @@
         <v>187</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>10</v>
@@ -12494,7 +12494,7 @@
         <v>189</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>10</v>
@@ -12601,7 +12601,7 @@
         <v>191</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>10</v>
@@ -12708,7 +12708,7 @@
         <v>193</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>10</v>
@@ -12815,7 +12815,7 @@
         <v>195</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>10</v>
@@ -12922,7 +12922,7 @@
         <v>197</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>10</v>
@@ -13029,7 +13029,7 @@
         <v>199</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>10</v>
@@ -13136,7 +13136,7 @@
         <v>201</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>10</v>
@@ -13243,7 +13243,7 @@
         <v>203</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>10</v>
@@ -13350,7 +13350,7 @@
         <v>205</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>10</v>
@@ -13457,7 +13457,7 @@
         <v>207</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>10</v>
@@ -13564,7 +13564,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>10</v>
@@ -13671,7 +13671,7 @@
         <v>211</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>10</v>
@@ -13778,7 +13778,7 @@
         <v>213</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>10</v>
@@ -13885,7 +13885,7 @@
         <v>215</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>10</v>
@@ -13992,7 +13992,7 @@
         <v>217</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>10</v>
@@ -14099,7 +14099,7 @@
         <v>219</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>10</v>
@@ -14206,7 +14206,7 @@
         <v>220</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>10</v>
@@ -14313,7 +14313,7 @@
         <v>222</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>10</v>
@@ -14420,7 +14420,7 @@
         <v>224</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>10</v>
@@ -14527,7 +14527,7 @@
         <v>226</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>10</v>
@@ -14634,7 +14634,7 @@
         <v>228</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>10</v>
@@ -14741,7 +14741,7 @@
         <v>230</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>10</v>
@@ -14848,7 +14848,7 @@
         <v>232</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>10</v>
@@ -14955,7 +14955,7 @@
         <v>234</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>10</v>
@@ -15062,7 +15062,7 @@
         <v>236</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>10</v>
@@ -15169,7 +15169,7 @@
         <v>238</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>10</v>
@@ -15276,7 +15276,7 @@
         <v>240</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>10</v>
@@ -15383,7 +15383,7 @@
         <v>242</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>10</v>
@@ -15490,7 +15490,7 @@
         <v>244</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>10</v>
@@ -15597,7 +15597,7 @@
         <v>246</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>248</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>10</v>
@@ -15811,7 +15811,7 @@
         <v>250</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>10</v>
@@ -15918,7 +15918,7 @@
         <v>252</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>10</v>
@@ -16025,7 +16025,7 @@
         <v>254</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>10</v>
@@ -16132,7 +16132,7 @@
         <v>256</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>10</v>
@@ -16239,7 +16239,7 @@
         <v>258</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>10</v>
@@ -16346,7 +16346,7 @@
         <v>260</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>10</v>
@@ -16453,7 +16453,7 @@
         <v>262</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>10</v>
@@ -16560,7 +16560,7 @@
         <v>264</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>10</v>
@@ -16667,7 +16667,7 @@
         <v>265</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>10</v>
@@ -16774,7 +16774,7 @@
         <v>267</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>10</v>
@@ -16881,7 +16881,7 @@
         <v>269</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>10</v>
@@ -16988,7 +16988,7 @@
         <v>271</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>10</v>
@@ -17095,7 +17095,7 @@
         <v>273</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>10</v>
@@ -17202,7 +17202,7 @@
         <v>275</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>10</v>
@@ -17309,7 +17309,7 @@
         <v>277</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>10</v>
@@ -17416,7 +17416,7 @@
         <v>279</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>10</v>
@@ -17523,7 +17523,7 @@
         <v>281</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>10</v>
@@ -17630,7 +17630,7 @@
         <v>283</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>10</v>
@@ -17737,7 +17737,7 @@
         <v>285</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>10</v>
@@ -17844,7 +17844,7 @@
         <v>287</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>10</v>
@@ -17951,7 +17951,7 @@
         <v>289</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>10</v>
@@ -18058,7 +18058,7 @@
         <v>291</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>10</v>
@@ -18165,7 +18165,7 @@
         <v>293</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>10</v>
@@ -18272,7 +18272,7 @@
         <v>295</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>10</v>
@@ -18379,7 +18379,7 @@
         <v>296</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>10</v>
@@ -18486,7 +18486,7 @@
         <v>298</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>10</v>
@@ -18593,7 +18593,7 @@
         <v>300</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>10</v>
@@ -18700,7 +18700,7 @@
         <v>302</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>10</v>
@@ -18807,7 +18807,7 @@
         <v>304</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>10</v>
@@ -18914,7 +18914,7 @@
         <v>306</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>10</v>
@@ -19021,7 +19021,7 @@
         <v>307</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>10</v>
@@ -19128,7 +19128,7 @@
         <v>308</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>10</v>
@@ -19235,7 +19235,7 @@
         <v>310</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>10</v>
@@ -19342,7 +19342,7 @@
         <v>312</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>10</v>
@@ -19449,7 +19449,7 @@
         <v>314</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>10</v>
@@ -19556,7 +19556,7 @@
         <v>316</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>10</v>
@@ -19663,7 +19663,7 @@
         <v>318</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>10</v>
@@ -19770,7 +19770,7 @@
         <v>320</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>10</v>
@@ -19877,7 +19877,7 @@
         <v>322</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>10</v>
@@ -19984,7 +19984,7 @@
         <v>324</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>10</v>
@@ -20091,7 +20091,7 @@
         <v>325</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>10</v>
@@ -20198,7 +20198,7 @@
         <v>326</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>10</v>
@@ -20305,7 +20305,7 @@
         <v>328</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>10</v>
@@ -20412,7 +20412,7 @@
         <v>329</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>10</v>
@@ -20519,7 +20519,7 @@
         <v>331</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>10</v>
@@ -20626,7 +20626,7 @@
         <v>333</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>10</v>
@@ -20733,7 +20733,7 @@
         <v>335</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>10</v>
@@ -20840,7 +20840,7 @@
         <v>337</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>10</v>
@@ -20947,7 +20947,7 @@
         <v>339</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>10</v>
@@ -21054,7 +21054,7 @@
         <v>340</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>10</v>
@@ -21161,7 +21161,7 @@
         <v>342</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>10</v>
@@ -21268,7 +21268,7 @@
         <v>343</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>10</v>
@@ -21375,7 +21375,7 @@
         <v>344</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>10</v>
@@ -21482,7 +21482,7 @@
         <v>346</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>10</v>
@@ -21589,7 +21589,7 @@
         <v>347</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>10</v>
@@ -21696,7 +21696,7 @@
         <v>348</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>10</v>
@@ -21803,7 +21803,7 @@
         <v>349</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>10</v>
@@ -21910,7 +21910,7 @@
         <v>350</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>10</v>
@@ -22017,7 +22017,7 @@
         <v>352</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>10</v>
@@ -22124,7 +22124,7 @@
         <v>354</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>10</v>
@@ -22338,7 +22338,7 @@
         <v>358</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>10</v>
@@ -22445,7 +22445,7 @@
         <v>360</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>10</v>
@@ -22552,7 +22552,7 @@
         <v>362</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>10</v>
@@ -22659,7 +22659,7 @@
         <v>364</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>10</v>
@@ -22766,7 +22766,7 @@
         <v>366</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>10</v>
@@ -22873,7 +22873,7 @@
         <v>368</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>10</v>
@@ -22980,7 +22980,7 @@
         <v>369</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>10</v>
@@ -23087,7 +23087,7 @@
         <v>371</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>10</v>
@@ -23194,7 +23194,7 @@
         <v>373</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>10</v>
@@ -23301,7 +23301,7 @@
         <v>375</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>10</v>
@@ -23515,7 +23515,7 @@
         <v>378</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>10</v>
@@ -23622,7 +23622,7 @@
         <v>380</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>10</v>
@@ -23836,7 +23836,7 @@
         <v>383</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>10</v>
@@ -23943,7 +23943,7 @@
         <v>385</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>10</v>
@@ -24050,7 +24050,7 @@
         <v>387</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>10</v>
@@ -24157,7 +24157,7 @@
         <v>389</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>10</v>
@@ -24264,7 +24264,7 @@
         <v>390</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>10</v>
@@ -24371,7 +24371,7 @@
         <v>391</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>10</v>
@@ -24478,7 +24478,7 @@
         <v>393</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>10</v>
@@ -24585,7 +24585,7 @@
         <v>394</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>10</v>
@@ -24692,7 +24692,7 @@
         <v>396</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>10</v>
@@ -24906,7 +24906,7 @@
         <v>394</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>10</v>
@@ -26083,7 +26083,7 @@
         <v>419</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>10</v>
@@ -26404,7 +26404,7 @@
         <v>422</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>10</v>
@@ -26511,7 +26511,7 @@
         <v>423</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>10</v>
@@ -26618,7 +26618,7 @@
         <v>369</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>10</v>
@@ -26725,7 +26725,7 @@
         <v>426</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>10</v>
@@ -26832,7 +26832,7 @@
         <v>428</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>10</v>
@@ -26939,7 +26939,7 @@
         <v>429</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>10</v>
@@ -27046,7 +27046,7 @@
         <v>431</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>10</v>
@@ -27153,7 +27153,7 @@
         <v>432</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>10</v>
@@ -27260,7 +27260,7 @@
         <v>433</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>10</v>
@@ -27367,7 +27367,7 @@
         <v>434</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>10</v>
@@ -27474,7 +27474,7 @@
         <v>435</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>10</v>
@@ -27581,7 +27581,7 @@
         <v>436</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>10</v>
@@ -27688,7 +27688,7 @@
         <v>437</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>10</v>
@@ -27795,7 +27795,7 @@
         <v>438</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>10</v>
@@ -27902,7 +27902,7 @@
         <v>439</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>10</v>
@@ -28009,7 +28009,7 @@
         <v>440</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E240" s="4" t="s">
         <v>10</v>
@@ -28116,7 +28116,7 @@
         <v>441</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>10</v>
@@ -28223,7 +28223,7 @@
         <v>442</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E242" s="4" t="s">
         <v>10</v>
@@ -28330,7 +28330,7 @@
         <v>443</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>10</v>
@@ -28437,7 +28437,7 @@
         <v>444</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E244" s="4" t="s">
         <v>10</v>
@@ -28544,7 +28544,7 @@
         <v>445</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E245" s="4" t="s">
         <v>10</v>
@@ -28651,7 +28651,7 @@
         <v>446</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E246" s="4" t="s">
         <v>10</v>
@@ -28758,7 +28758,7 @@
         <v>447</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>10</v>
@@ -28865,7 +28865,7 @@
         <v>448</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>10</v>
@@ -28972,7 +28972,7 @@
         <v>449</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>10</v>
@@ -29079,7 +29079,7 @@
         <v>450</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>10</v>
@@ -29186,7 +29186,7 @@
         <v>451</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>10</v>
@@ -29507,7 +29507,7 @@
         <v>454</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E254" s="4" t="s">
         <v>10</v>
@@ -29614,7 +29614,7 @@
         <v>376</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E255" s="4" t="s">
         <v>10</v>
@@ -29721,7 +29721,7 @@
         <v>456</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>10</v>
@@ -29828,7 +29828,7 @@
         <v>457</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E257" s="4" t="s">
         <v>10</v>
@@ -29935,7 +29935,7 @@
         <v>458</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E258" s="4" t="s">
         <v>10</v>
@@ -30042,7 +30042,7 @@
         <v>459</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E259" s="4" t="s">
         <v>10</v>
@@ -30149,7 +30149,7 @@
         <v>460</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E260" s="4" t="s">
         <v>10</v>
@@ -30256,7 +30256,7 @@
         <v>461</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>10</v>
@@ -30363,7 +30363,7 @@
         <v>463</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E262" s="4" t="s">
         <v>10</v>
@@ -30470,7 +30470,7 @@
         <v>464</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>10</v>
@@ -30577,7 +30577,7 @@
         <v>465</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E264" s="4" t="s">
         <v>10</v>
@@ -30684,7 +30684,7 @@
         <v>466</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E265" s="4" t="s">
         <v>10</v>
@@ -30791,7 +30791,7 @@
         <v>467</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>10</v>
@@ -30898,7 +30898,7 @@
         <v>468</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>10</v>
@@ -31005,7 +31005,7 @@
         <v>469</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E268" s="4" t="s">
         <v>10</v>
@@ -31219,7 +31219,7 @@
         <v>473</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E270" s="4" t="s">
         <v>10</v>
@@ -31326,7 +31326,7 @@
         <v>474</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E271" s="4" t="s">
         <v>10</v>
@@ -31433,7 +31433,7 @@
         <v>475</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E272" s="4" t="s">
         <v>10</v>
@@ -31540,7 +31540,7 @@
         <v>476</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E273" s="4" t="s">
         <v>10</v>
@@ -31647,7 +31647,7 @@
         <v>478</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E274" s="4" t="s">
         <v>10</v>
@@ -31861,7 +31861,7 @@
         <v>480</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E276" s="4" t="s">
         <v>10</v>
@@ -31968,7 +31968,7 @@
         <v>481</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>10</v>
@@ -32075,7 +32075,7 @@
         <v>482</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E278" s="4" t="s">
         <v>10</v>
@@ -32182,7 +32182,7 @@
         <v>483</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>10</v>
@@ -32289,7 +32289,7 @@
         <v>485</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>10</v>
@@ -32396,7 +32396,7 @@
         <v>487</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E281" s="4" t="s">
         <v>10</v>
@@ -32503,7 +32503,7 @@
         <v>488</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E282" s="4" t="s">
         <v>10</v>
@@ -32610,7 +32610,7 @@
         <v>489</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E283" s="4" t="s">
         <v>10</v>
@@ -32717,7 +32717,7 @@
         <v>490</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E284" s="4" t="s">
         <v>10</v>
@@ -32824,7 +32824,7 @@
         <v>491</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E285" s="4" t="s">
         <v>10</v>
@@ -32931,7 +32931,7 @@
         <v>492</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E286" s="4" t="s">
         <v>10</v>
@@ -33038,7 +33038,7 @@
         <v>493</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E287" s="4" t="s">
         <v>10</v>
@@ -33252,7 +33252,7 @@
         <v>496</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E289" s="4" t="s">
         <v>10</v>
@@ -33359,7 +33359,7 @@
         <v>497</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E290" s="4" t="s">
         <v>10</v>
@@ -33466,7 +33466,7 @@
         <v>499</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E291" s="4" t="s">
         <v>10</v>
@@ -33573,7 +33573,7 @@
         <v>500</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E292" s="4" t="s">
         <v>10</v>
@@ -33680,7 +33680,7 @@
         <v>502</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E293" s="4" t="s">
         <v>10</v>
@@ -33787,7 +33787,7 @@
         <v>503</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E294" s="4" t="s">
         <v>10</v>
@@ -33894,7 +33894,7 @@
         <v>505</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>10</v>
@@ -34108,7 +34108,7 @@
         <v>508</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E297" s="4" t="s">
         <v>10</v>
@@ -34215,7 +34215,7 @@
         <v>510</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E298" s="4" t="s">
         <v>10</v>
@@ -34429,7 +34429,7 @@
         <v>513</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E300" s="4" t="s">
         <v>10</v>
@@ -34536,7 +34536,7 @@
         <v>514</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E301" s="4" t="s">
         <v>10</v>
@@ -34643,7 +34643,7 @@
         <v>515</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E302" s="4" t="s">
         <v>10</v>
@@ -34750,7 +34750,7 @@
         <v>516</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E303" s="4" t="s">
         <v>10</v>
@@ -34857,7 +34857,7 @@
         <v>517</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E304" s="4" t="s">
         <v>10</v>
@@ -34964,7 +34964,7 @@
         <v>518</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E305" s="4" t="s">
         <v>10</v>
@@ -35071,7 +35071,7 @@
         <v>519</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>10</v>
@@ -35178,7 +35178,7 @@
         <v>520</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E307" s="4" t="s">
         <v>10</v>
@@ -35285,7 +35285,7 @@
         <v>521</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E308" s="4" t="s">
         <v>10</v>
@@ -35392,7 +35392,7 @@
         <v>522</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E309" s="4" t="s">
         <v>10</v>
@@ -35499,7 +35499,7 @@
         <v>523</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E310" s="4" t="s">
         <v>10</v>
@@ -35606,7 +35606,7 @@
         <v>524</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E311" s="4" t="s">
         <v>10</v>
@@ -35713,7 +35713,7 @@
         <v>526</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E312" s="4" t="s">
         <v>10</v>
@@ -35820,7 +35820,7 @@
         <v>528</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E313" s="4" t="s">
         <v>10</v>
@@ -35927,7 +35927,7 @@
         <v>530</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E314" s="4" t="s">
         <v>10</v>
@@ -36034,7 +36034,7 @@
         <v>531</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>10</v>
@@ -36141,7 +36141,7 @@
         <v>532</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E316" s="4" t="s">
         <v>10</v>
@@ -36248,7 +36248,7 @@
         <v>533</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E317" s="4" t="s">
         <v>10</v>
@@ -36355,7 +36355,7 @@
         <v>534</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E318" s="4" t="s">
         <v>10</v>
@@ -36462,7 +36462,7 @@
         <v>535</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E319" s="4" t="s">
         <v>10</v>
@@ -36569,7 +36569,7 @@
         <v>536</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E320" s="4" t="s">
         <v>10</v>
@@ -36997,7 +36997,7 @@
         <v>344</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E324" s="4" t="s">
         <v>10</v>
@@ -37104,7 +37104,7 @@
         <v>543</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E325" s="4" t="s">
         <v>10</v>
@@ -37211,7 +37211,7 @@
         <v>544</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E326" s="4" t="s">
         <v>10</v>
@@ -37318,7 +37318,7 @@
         <v>545</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E327" s="4" t="s">
         <v>10</v>
@@ -37425,7 +37425,7 @@
         <v>546</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E328" s="4" t="s">
         <v>10</v>
@@ -37532,7 +37532,7 @@
         <v>547</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>10</v>
@@ -37639,7 +37639,7 @@
         <v>548</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>10</v>
@@ -37746,7 +37746,7 @@
         <v>549</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E331" s="4" t="s">
         <v>10</v>
@@ -37853,7 +37853,7 @@
         <v>550</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E332" s="4" t="s">
         <v>10</v>
@@ -37960,7 +37960,7 @@
         <v>552</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E333" s="4" t="s">
         <v>10</v>
@@ -38174,7 +38174,7 @@
         <v>536</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E335" s="4" t="s">
         <v>10</v>
@@ -38281,7 +38281,7 @@
         <v>557</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E336" s="4" t="s">
         <v>10</v>
@@ -38388,7 +38388,7 @@
         <v>558</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E337" s="4" t="s">
         <v>10</v>
@@ -38495,7 +38495,7 @@
         <v>560</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E338" s="4" t="s">
         <v>10</v>
